--- a/poc/Annotations/Annotation_Hertz_Sixt_Goldcar.xlsx
+++ b/poc/Annotations/Annotation_Hertz_Sixt_Goldcar.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dilia\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d152c42fb0787e8e/IronHack/Projects/final-project-Dilia-Navarro/poc/Annotations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F18CED76-5733-4F46-8BD7-B91E12302B12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{F18CED76-5733-4F46-8BD7-B91E12302B12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{66D21E26-DD1E-40D8-963A-BB437F786E66}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="HERTZ_ES" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="367">
   <si>
     <t>SUPPLIER:</t>
   </si>
@@ -1626,6 +1626,9 @@
 Si su licencia de conducir española ha sido extraviada o sustraída, ha caducado o está siendo renovada no será posible efectuar alquileres con Hertz. Se requiere presentar la licencia original en vigor, no pudiendo aceptarse ni fotocopias ni resguardos o comprobantes expedidos por las autoridades españolas, ya sea para alquileres nacionales o internacionales.
 Aunque Hertz no siempre insiste en la presentación de un Permiso Internacional de Conducción (IDP), siempre sujeto a la presentación de una licencia de conducir nacional válida, las leyes locales de algunos países pueden requerir a los conductores extranjeros la posesión del Permiso de Conducir Internacional. La falta de la presentación del Permiso de Conducción Internacional a las autoridades locales podría incurrir en una infracción que pudiera ser sancionada con una multa o la inmovilización del vehículo. Por ello, le recomendamos encarecidamente que se asegure de los requerimientos legales del país donde desea circular.
 Los términos y condiciones varían en función del destino. Los términos &amp; condiciones de alquiler de cada oficina se encuentran en nuestra página web (Sección: "Oficinas y flota" - Optar por la oficina en que desea alquilar - "Información adicional de la oficina" - "Términos &amp; Condiciones" - "Licencia de conducir").</t>
+  </si>
+  <si>
+    <t>Mietbedingungen</t>
   </si>
 </sst>
 </file>
@@ -3430,7 +3433,7 @@
       <c r="C44" s="19"/>
       <c r="D44" s="19"/>
     </row>
-    <row r="45" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45" s="19" t="s">
         <v>49</v>
       </c>
@@ -3444,7 +3447,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A46" s="19" t="s">
         <v>55</v>
       </c>
@@ -3458,7 +3461,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A47" s="19" t="s">
         <v>58</v>
       </c>
@@ -3468,7 +3471,7 @@
       <c r="C47" s="19"/>
       <c r="D47" s="19"/>
     </row>
-    <row r="48" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A48" s="19" t="s">
         <v>183</v>
       </c>
@@ -3504,7 +3507,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="51" spans="1:4" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A51" s="19" t="s">
         <v>52</v>
       </c>
@@ -3532,7 +3535,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="53" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A53" s="19" t="s">
         <v>58</v>
       </c>
@@ -3542,7 +3545,7 @@
       <c r="C53" s="19"/>
       <c r="D53" s="19"/>
     </row>
-    <row r="54" spans="1:4" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A54" s="19" t="s">
         <v>61</v>
       </c>
@@ -3560,7 +3563,7 @@
       <c r="C55" s="19"/>
       <c r="D55" s="19"/>
     </row>
-    <row r="56" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56" s="19" t="s">
         <v>58</v>
       </c>
@@ -3570,7 +3573,7 @@
       <c r="C56" s="19"/>
       <c r="D56" s="19"/>
     </row>
-    <row r="57" spans="1:4" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A57" s="19" t="s">
         <v>197</v>
       </c>
@@ -3592,7 +3595,7 @@
       <c r="C58" s="19"/>
       <c r="D58" s="19"/>
     </row>
-    <row r="59" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A59" s="19" t="s">
         <v>123</v>
       </c>
@@ -3602,7 +3605,7 @@
       <c r="C59" s="19"/>
       <c r="D59" s="19"/>
     </row>
-    <row r="60" spans="1:4" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A60" s="19" t="s">
         <v>201</v>
       </c>
@@ -3616,7 +3619,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="61" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A61" s="19" t="s">
         <v>204</v>
       </c>
@@ -3638,7 +3641,7 @@
       <c r="C62" s="19"/>
       <c r="D62" s="19"/>
     </row>
-    <row r="63" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A63" s="19" t="s">
         <v>207</v>
       </c>
@@ -3648,7 +3651,7 @@
       <c r="C63" s="19"/>
       <c r="D63" s="19"/>
     </row>
-    <row r="64" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A64" s="19" t="s">
         <v>123</v>
       </c>
@@ -3662,7 +3665,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="65" spans="1:4" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A65" s="19" t="s">
         <v>211</v>
       </c>
@@ -4459,8 +4462,11 @@
       <c r="A26" t="s">
         <v>358</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="1" t="s">
         <v>359</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>366</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
@@ -4690,9 +4696,13 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C26" r:id="rId1" display="https://www.hertz.com/rentacar/reservation/reviewmodifycancel/templates/rentalTerms.jsp?KEYWORD=PICKUP&amp;EOAG=USNT50" xr:uid="{6AB1DD97-CCD7-4DFE-90EF-BE8941BDF27F}"/>
+    <hyperlink ref="B26" r:id="rId2" xr:uid="{382420C0-3AEA-4C57-A20F-520509B8BE6A}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
+  <drawing r:id="rId4"/>
 </worksheet>
 </file>
 
